--- a/src/xlsx/buildingsB.xlsx
+++ b/src/xlsx/buildingsB.xlsx
@@ -3625,6 +3625,7 @@
       </c>
       <c r="G102" s="1" t="n"/>
     </row>
+    <row r="103"/>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
@@ -5388,6 +5389,7 @@
         </is>
       </c>
     </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
@@ -6316,6 +6318,7 @@
       </c>
       <c r="O17" s="1" t="n"/>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
@@ -8641,6 +8644,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -9226,6 +9230,7 @@
         </is>
       </c>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -13480,6 +13485,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -15912,6 +15918,7 @@
       <c r="J103" s="1" t="n"/>
       <c r="K103" s="1" t="n"/>
     </row>
+    <row r="104"/>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
@@ -18124,6 +18131,7 @@
         </is>
       </c>
     </row>
+    <row r="169"/>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
@@ -18320,6 +18328,7 @@
         </is>
       </c>
     </row>
+    <row r="175"/>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
@@ -21725,6 +21734,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="B26" t="inlineStr">
         <is>
@@ -21768,6 +21778,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
@@ -22019,6 +22030,7 @@
       <c r="J37" s="1" t="n"/>
       <c r="K37" s="1" t="n"/>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -25365,6 +25377,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="B32" t="inlineStr">
         <is>
@@ -25377,6 +25390,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
@@ -25420,6 +25434,7 @@
         </is>
       </c>
     </row>
+    <row r="38"/>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
@@ -25957,6 +25972,7 @@
         </is>
       </c>
     </row>
+    <row r="52"/>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
@@ -28026,6 +28042,7 @@
         </is>
       </c>
     </row>
+    <row r="106"/>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
@@ -28990,6 +29007,7 @@
         </is>
       </c>
     </row>
+    <row r="132"/>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
@@ -30176,6 +30194,7 @@
       </c>
       <c r="K19" s="1" t="n"/>
     </row>
+    <row r="20"/>
     <row r="21">
       <c r="B21" t="inlineStr">
         <is>
@@ -30207,6 +30226,7 @@
         </is>
       </c>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
@@ -33329,6 +33349,7 @@
         </is>
       </c>
     </row>
+    <row r="25"/>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
@@ -33493,6 +33514,7 @@
       </c>
       <c r="G30" s="1" t="n"/>
     </row>
+    <row r="31"/>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
@@ -33788,6 +33810,7 @@
       </c>
       <c r="K40" s="1" t="n"/>
     </row>
+    <row r="41"/>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
@@ -43999,6 +44022,7 @@
       </c>
       <c r="G48" s="1" t="n"/>
     </row>
+    <row r="49"/>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
@@ -44161,6 +44185,7 @@
       </c>
       <c r="G56" s="1" t="n"/>
     </row>
+    <row r="57"/>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
@@ -44279,6 +44304,7 @@
         </is>
       </c>
     </row>
+    <row r="62"/>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
@@ -45155,6 +45181,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
@@ -45875,6 +45902,7 @@
         </is>
       </c>
     </row>
+    <row r="47"/>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
@@ -46326,6 +46354,7 @@
       </c>
       <c r="K60" s="1" t="n"/>
     </row>
+    <row r="61"/>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
@@ -46848,6 +46877,7 @@
         </is>
       </c>
     </row>
+    <row r="74"/>
     <row r="75">
       <c r="B75" t="inlineStr">
         <is>
@@ -46879,6 +46909,7 @@
         </is>
       </c>
     </row>
+    <row r="78"/>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
@@ -47634,6 +47665,7 @@
         </is>
       </c>
     </row>
+    <row r="100"/>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
@@ -49109,6 +49141,7 @@
       </c>
       <c r="K27" s="1" t="n"/>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>

--- a/src/xlsx/buildingsB.xlsx
+++ b/src/xlsx/buildingsB.xlsx
@@ -8162,7 +8162,7 @@
       </c>
       <c r="G9" s="1" t="inlineStr">
         <is>
-          <t>我還挺擔心的來著。</t>
+          <t>我還滿擔心的。</t>
         </is>
       </c>
       <c r="I9" s="1" t="inlineStr">
@@ -9261,7 +9261,7 @@
       </c>
       <c r="G43" s="1" t="inlineStr">
         <is>
-          <t>你的持有物滿了喲。</t>
+          <t>你的背包滿了喔。</t>
         </is>
       </c>
       <c r="I43" s="1" t="inlineStr">
@@ -15569,7 +15569,7 @@
       </c>
       <c r="G93" s="1" t="inlineStr">
         <is>
-          <t>一味地四處溜達</t>
+          <t>光是在這裡亂晃</t>
         </is>
       </c>
       <c r="I93" s="1" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="G94" s="1" t="inlineStr">
         <is>
-          <t>是無濟於事的。</t>
+          <t>是沒用的。</t>
         </is>
       </c>
       <c r="I94" s="1" t="inlineStr">
@@ -17731,7 +17731,7 @@
       </c>
       <c r="G158" s="1" t="inlineStr">
         <is>
-          <t>讓你挺頭疼的啊！</t>
+          <t>讓你吃了不少苦頭啊！</t>
         </is>
       </c>
       <c r="I158" s="1" t="inlineStr">
@@ -17829,7 +17829,7 @@
       </c>
       <c r="G160" s="1" t="inlineStr">
         <is>
-          <t>這和本大爺沒關係！</t>
+          <t>這和本少爺沒關係！</t>
         </is>
       </c>
       <c r="I160" s="1" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="G187" s="1" t="inlineStr">
         <is>
-          <t>本大爺要</t>
+          <t>本少爺要</t>
         </is>
       </c>
       <c r="I187" s="1" t="inlineStr">
@@ -19095,7 +19095,7 @@
       </c>
       <c r="G194" s="1" t="inlineStr">
         <is>
-          <t>得，就說到這吧。</t>
+          <t>好，就說到這吧。</t>
         </is>
       </c>
       <c r="I194" s="1" t="inlineStr">
@@ -24235,7 +24235,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>&lt;RIVAL&gt;：喲！</t>
+          <t>&lt;RIVAL&gt;：嘿！</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -25243,7 +25243,7 @@
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>本大爺是天下第一！</t>
+          <t>本少爺是天下第一！</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -25280,7 +25280,7 @@
       </c>
       <c r="G25" s="1" t="inlineStr">
         <is>
-          <t>本大爺最強最厲害！</t>
+          <t>本少爺最強最厲害！</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -26107,7 +26107,7 @@
       </c>
       <c r="G56" s="1" t="inlineStr">
         <is>
-          <t>本大爺怎麼可能</t>
+          <t>本少爺怎麼可能</t>
         </is>
       </c>
       <c r="I56" s="1" t="inlineStr">
@@ -32633,7 +32633,7 @@
       </c>
       <c r="G5" s="1" t="inlineStr">
         <is>
-          <t>十分疼愛你啊！</t>
+          <t>很看重你啊！</t>
         </is>
       </c>
       <c r="I5" s="1" t="inlineStr">
@@ -32780,7 +32780,7 @@
       </c>
       <c r="G8" s="1" t="inlineStr">
         <is>
-          <t>強大的好男人！</t>
+          <t>又強又帥的男人！</t>
         </is>
       </c>
       <c r="I8" s="1" t="inlineStr">
@@ -34782,7 +34782,7 @@
       </c>
       <c r="G24" s="1" t="inlineStr">
         <is>
-          <t>我在力量上輸了麼！</t>
+          <t>力量輸給你了嗎！</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -39324,7 +39324,7 @@
       </c>
       <c r="G18" s="1" t="inlineStr">
         <is>
-          <t>在氣勢上輸了麼。</t>
+          <t>氣勢還不夠嗎。</t>
         </is>
       </c>
       <c r="I18" s="1" t="inlineStr">
@@ -40650,7 +40650,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>你看上去很累呢！</t>
+          <t>你好像很累呢！</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -44587,7 +44587,7 @@
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>社長：喔～！小夥子！</t>
+          <t>社長：喔～！小兄弟！</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
@@ -45933,7 +45933,7 @@
       </c>
       <c r="G49" s="1" t="inlineStr">
         <is>
-          <t>持有物已滿了哦。</t>
+          <t>背包已滿了哦。</t>
         </is>
       </c>
       <c r="I49" s="1" t="inlineStr">
@@ -46693,7 +46693,7 @@
       </c>
       <c r="G69" s="1" t="inlineStr">
         <is>
-          <t>瞎摻和了！</t>
+          <t>插手管閒事了！</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
